--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -1,27 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenSource\GF_X\AAAGameData\DataTables\Core\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120"/>
+    <workbookView windowWidth="21480" windowHeight="7785"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
   <si>
     <t>#</t>
   </si>
@@ -41,6 +49,9 @@
     <t>PauseCoveredUI</t>
   </si>
   <si>
+    <t>UIGroupId</t>
+  </si>
+  <si>
     <t>EscapeClose</t>
   </si>
   <si>
@@ -53,116 +64,14 @@
     <t>bool</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>游戏界面</t>
-  </si>
-  <si>
-    <t>GameUIForm</t>
-  </si>
-  <si>
-    <t>SettingDialog</t>
-  </si>
-  <si>
-    <t>CommonDialog</t>
-  </si>
-  <si>
-    <t>ToastTips</t>
-  </si>
-  <si>
-    <t>GameOverUIForm</t>
-  </si>
-  <si>
-    <t>MenuUIForm</t>
-  </si>
-  <si>
-    <t>返回键触发关闭界面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LanguagesDialog</t>
-  </si>
-  <si>
-    <t>RatingDialog</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TermsOfServiceDialog</t>
-  </si>
-  <si>
-    <t>同组界面被覆盖时是否隐藏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Topbar</t>
-  </si>
-  <si>
-    <t>主菜单</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏结算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>顶部资源栏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>评分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>服务条款</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用提示对话框</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语言设置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吐司提示</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>提示(顶层)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话框(中层)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主界面(顶层)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>显示顺序,相对于Group,每个Group间隔100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UIGroupId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>i</t>
     </r>
     <r>
@@ -170,24 +79,114 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>nt</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>显示顺序,相对于Group,每个Group间隔100</t>
+  </si>
+  <si>
+    <t>同组界面被覆盖时是否隐藏</t>
   </si>
   <si>
     <t>UI组Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回键触发关闭界面</t>
+  </si>
+  <si>
+    <t>主界面(顶层)</t>
+  </si>
+  <si>
+    <t>主菜单</t>
+  </si>
+  <si>
+    <t>MenuUIForm</t>
+  </si>
+  <si>
+    <t>游戏界面</t>
+  </si>
+  <si>
+    <t>GameUIForm</t>
+  </si>
+  <si>
+    <t>游戏结算</t>
+  </si>
+  <si>
+    <t>GameOverUIForm</t>
+  </si>
+  <si>
+    <t>顶部资源栏</t>
+  </si>
+  <si>
+    <t>Topbar</t>
+  </si>
+  <si>
+    <t>对话框(中层)</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>SettingDialog</t>
+  </si>
+  <si>
+    <t>评分</t>
+  </si>
+  <si>
+    <t>RatingDialog</t>
+  </si>
+  <si>
+    <t>服务条款</t>
+  </si>
+  <si>
+    <t>TermsOfServiceDialog</t>
+  </si>
+  <si>
+    <t>通用提示对话框</t>
+  </si>
+  <si>
+    <t>CommonDialog</t>
+  </si>
+  <si>
+    <t>语言设置</t>
+  </si>
+  <si>
+    <t>LanguagesDialog</t>
+  </si>
+  <si>
+    <t>合成面板</t>
+  </si>
+  <si>
+    <t>CraftingDialog</t>
+  </si>
+  <si>
+    <t>提示(顶层)</t>
+  </si>
+  <si>
+    <t>吐司提示</t>
+  </si>
+  <si>
+    <t>ToastTips</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,29 +195,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -226,25 +548,311 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -293,7 +901,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -328,7 +936,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -531,25 +1139,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="40.125" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -557,7 +1165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -574,78 +1182,78 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:8">
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -657,18 +1265,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:8">
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -680,18 +1288,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:8">
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -703,18 +1311,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:8">
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -726,17 +1334,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:8">
       <c r="B11">
         <v>5</v>
       </c>
@@ -747,7 +1355,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -759,18 +1367,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8">
       <c r="B12">
         <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -782,18 +1390,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:8">
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -805,18 +1413,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:8">
       <c r="B14">
         <v>8</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -828,18 +1436,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:8">
       <c r="B15">
         <v>9</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
@@ -851,61 +1459,87 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B17">
+    <row r="16" spans="1:8">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1">
+        <v>11</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="B18">
         <v>10</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" t="b">
+      <c r="C18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="b">
         <v>0</v>
       </c>
-      <c r="G17">
+      <c r="G18">
         <v>3</v>
       </c>
-      <c r="H17" t="b">
+      <c r="H18" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21480" windowHeight="7785"/>
+    <workbookView windowWidth="19200" windowHeight="8200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
   <si>
     <t>#</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>EscapeClose</t>
+  </si>
+  <si>
+    <t>BlockCharacterControl</t>
   </si>
   <si>
     <t>int</t>
@@ -101,6 +104,9 @@
     <t>返回键触发关闭界面</t>
   </si>
   <si>
+    <t>是否屏蔽角色控制</t>
+  </si>
+  <si>
     <t>主界面(顶层)</t>
   </si>
   <si>
@@ -128,6 +134,12 @@
     <t>Topbar</t>
   </si>
   <si>
+    <t>材料编辑栏</t>
+  </si>
+  <si>
+    <t>MaterialModifyBar</t>
+  </si>
+  <si>
     <t>对话框(中层)</t>
   </si>
   <si>
@@ -167,6 +179,18 @@
     <t>CraftingDialog</t>
   </si>
   <si>
+    <t>科技树</t>
+  </si>
+  <si>
+    <t>TechTreeDialog</t>
+  </si>
+  <si>
+    <t>科技节点详情</t>
+  </si>
+  <si>
+    <t>TechNodeDetailTips</t>
+  </si>
+  <si>
     <t>提示(顶层)</t>
   </si>
   <si>
@@ -174,6 +198,12 @@
   </si>
   <si>
     <t>ToastTips</t>
+  </si>
+  <si>
+    <t>交互选项</t>
+  </si>
+  <si>
+    <t>InteractOptionTips</t>
   </si>
 </sst>
 </file>
@@ -186,14 +216,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -664,139 +687,139 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1145,19 +1168,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="13.125" customWidth="1"/>
-    <col min="3" max="3" width="15.125" customWidth="1"/>
-    <col min="4" max="4" width="40.125" customWidth="1"/>
+    <col min="2" max="2" width="13.1272727272727" customWidth="1"/>
+    <col min="3" max="3" width="15.1272727272727" customWidth="1"/>
+    <col min="4" max="4" width="40.1272727272727" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="25.5" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="19.25" customWidth="1"/>
+    <col min="8" max="8" width="19.2545454545455" customWidth="1"/>
+    <col min="9" max="9" width="16.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1165,7 +1189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1187,48 +1211,57 @@
       <c r="H2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
         <v>11</v>
       </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1236,24 +1269,24 @@
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="2:9">
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -1264,19 +1297,22 @@
       <c r="H6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -1287,19 +1323,22 @@
       <c r="H7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -1310,19 +1349,22 @@
       <c r="H8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -1333,52 +1375,58 @@
       <c r="H9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="B11">
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="2:9">
+      <c r="B10">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="B12">
         <v>5</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="B12">
-        <v>6</v>
-      </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -1389,19 +1437,22 @@
       <c r="H12" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
       <c r="B13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
-      <c r="E13" t="s">
-        <v>32</v>
+      <c r="E13" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -1412,19 +1463,22 @@
       <c r="H13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
       <c r="B14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -1433,48 +1487,53 @@
         <v>2</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
       <c r="B15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>2</v>
       </c>
       <c r="H15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16">
+        <v>9</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1482,36 +1541,149 @@
       <c r="H16" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="B18">
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21">
         <v>10</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18">
+      <c r="C21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21">
         <v>3</v>
       </c>
-      <c r="H18" t="b">
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1526,7 +1698,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1537,7 +1709,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -1,27 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenSource\GF_X\AAAGameData\DataTables\Core\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
   <si>
     <t>#</t>
   </si>
@@ -41,6 +49,9 @@
     <t>PauseCoveredUI</t>
   </si>
   <si>
+    <t>UIGroupId</t>
+  </si>
+  <si>
     <t>EscapeClose</t>
   </si>
   <si>
@@ -53,116 +64,14 @@
     <t>bool</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>游戏界面</t>
-  </si>
-  <si>
-    <t>GameUIForm</t>
-  </si>
-  <si>
-    <t>SettingDialog</t>
-  </si>
-  <si>
-    <t>CommonDialog</t>
-  </si>
-  <si>
-    <t>ToastTips</t>
-  </si>
-  <si>
-    <t>GameOverUIForm</t>
-  </si>
-  <si>
-    <t>MenuUIForm</t>
-  </si>
-  <si>
-    <t>返回键触发关闭界面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LanguagesDialog</t>
-  </si>
-  <si>
-    <t>RatingDialog</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TermsOfServiceDialog</t>
-  </si>
-  <si>
-    <t>同组界面被覆盖时是否隐藏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Topbar</t>
-  </si>
-  <si>
-    <t>主菜单</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏结算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>顶部资源栏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>评分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>服务条款</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用提示对话框</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语言设置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吐司提示</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>提示(顶层)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话框(中层)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主界面(顶层)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>显示顺序,相对于Group,每个Group间隔100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UIGroupId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>i</t>
     </r>
     <r>
@@ -170,24 +79,114 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>nt</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>显示顺序,相对于Group,每个Group间隔100</t>
+  </si>
+  <si>
+    <t>同组界面被覆盖时是否隐藏</t>
   </si>
   <si>
     <t>UI组Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回键触发关闭界面</t>
+  </si>
+  <si>
+    <t>主界面(顶层)</t>
+  </si>
+  <si>
+    <t>主菜单</t>
+  </si>
+  <si>
+    <t>MenuUIForm</t>
+  </si>
+  <si>
+    <t>游戏界面</t>
+  </si>
+  <si>
+    <t>GameUIForm</t>
+  </si>
+  <si>
+    <t>游戏结算</t>
+  </si>
+  <si>
+    <t>GameOverUIForm</t>
+  </si>
+  <si>
+    <t>顶部资源栏</t>
+  </si>
+  <si>
+    <t>Topbar</t>
+  </si>
+  <si>
+    <t>对话框(中层)</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>SettingDialog</t>
+  </si>
+  <si>
+    <t>评分</t>
+  </si>
+  <si>
+    <t>RatingDialog</t>
+  </si>
+  <si>
+    <t>服务条款</t>
+  </si>
+  <si>
+    <t>TermsOfServiceDialog</t>
+  </si>
+  <si>
+    <t>通用提示对话框</t>
+  </si>
+  <si>
+    <t>CommonDialog</t>
+  </si>
+  <si>
+    <t>语言设置</t>
+  </si>
+  <si>
+    <t>LanguagesDialog</t>
+  </si>
+  <si>
+    <t>提示(顶层)</t>
+  </si>
+  <si>
+    <t>吐司提示</t>
+  </si>
+  <si>
+    <t>ToastTips</t>
+  </si>
+  <si>
+    <t>UI交互</t>
+  </si>
+  <si>
+    <t>CardUIForm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,29 +195,358 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9.8"/>
+      <color rgb="FFD0D0D0"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -226,25 +554,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -293,7 +908,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -328,7 +943,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -531,25 +1146,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="40.125" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -557,7 +1172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -574,78 +1189,78 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:8">
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -657,18 +1272,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:8">
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -680,18 +1295,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:8">
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -703,18 +1318,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:8">
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -726,17 +1341,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:8">
       <c r="B11">
         <v>5</v>
       </c>
@@ -747,7 +1362,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -759,18 +1374,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8">
       <c r="B12">
         <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -782,18 +1397,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:8">
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -805,18 +1420,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:8">
       <c r="B14">
         <v>8</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -828,18 +1443,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:8">
       <c r="B15">
         <v>9</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
@@ -851,27 +1466,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17">
         <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
@@ -883,29 +1498,54 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18" spans="2:8">
+      <c r="B18">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8200"/>
+    <workbookView windowWidth="29100" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="宋体"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -81,7 +81,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="宋体"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -211,16 +211,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -228,7 +228,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -236,14 +236,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -251,7 +251,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -259,7 +259,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -267,7 +267,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -275,7 +275,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -283,14 +283,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -298,7 +298,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -306,7 +306,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -314,14 +314,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -329,42 +329,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -672,19 +672,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -822,55 +822,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1169,16 +1169,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="2" width="13.1272727272727" customWidth="1"/>
-    <col min="3" max="3" width="15.1272727272727" customWidth="1"/>
-    <col min="4" max="4" width="40.1272727272727" customWidth="1"/>
+    <col min="2" max="2" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="40.125" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="25.5" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="19.2545454545455" customWidth="1"/>
-    <col min="9" max="9" width="16.6363636363636" customWidth="1"/>
+    <col min="8" max="8" width="19.2578125" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" ht="17" spans="1:9">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1698,7 +1698,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1709,7 +1709,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8200"/>
+    <workbookView windowWidth="28800" windowHeight="11610"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
   <si>
     <t>#</t>
   </si>
@@ -204,6 +204,12 @@
   </si>
   <si>
     <t>InteractOptionTips</t>
+  </si>
+  <si>
+    <t>ui</t>
+  </si>
+  <si>
+    <t>CardUIForm</t>
   </si>
 </sst>
 </file>
@@ -1168,20 +1174,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="13.1272727272727" customWidth="1"/>
-    <col min="3" max="3" width="15.1272727272727" customWidth="1"/>
-    <col min="4" max="4" width="40.1272727272727" customWidth="1"/>
+    <col min="2" max="2" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="40.125" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="25.5" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="19.2545454545455" customWidth="1"/>
-    <col min="9" max="9" width="16.6363636363636" customWidth="1"/>
+    <col min="8" max="8" width="19.2583333333333" customWidth="1"/>
+    <col min="9" max="9" width="16.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1264,7 +1270,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -1275,7 +1281,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="2:9">
+    <row r="6" spans="1:9">
       <c r="B6">
         <v>1</v>
       </c>
@@ -1301,7 +1307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:9">
+    <row r="7" spans="1:9">
       <c r="B7">
         <v>2</v>
       </c>
@@ -1327,7 +1333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="1:9">
       <c r="B8">
         <v>3</v>
       </c>
@@ -1353,7 +1359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="1:9">
       <c r="B9">
         <v>4</v>
       </c>
@@ -1379,7 +1385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="2:9">
+    <row r="10" customFormat="1" spans="1:9">
       <c r="B10">
         <v>13</v>
       </c>
@@ -1405,7 +1411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1415,7 +1421,7 @@
       <c r="C11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="1:9">
       <c r="B12">
         <v>5</v>
       </c>
@@ -1441,7 +1447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="1:9">
       <c r="B13">
         <v>6</v>
       </c>
@@ -1467,7 +1473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="1:9">
       <c r="B14">
         <v>7</v>
       </c>
@@ -1493,7 +1499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:9">
+    <row r="15" spans="1:9">
       <c r="B15">
         <v>8</v>
       </c>
@@ -1519,7 +1525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:9">
+    <row r="16" spans="1:9">
       <c r="B16">
         <v>9</v>
       </c>
@@ -1626,7 +1632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -1635,7 +1641,7 @@
       </c>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="2:9">
+    <row r="21" spans="1:9">
       <c r="B21">
         <v>10</v>
       </c>
@@ -1661,7 +1667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:9">
+    <row r="22" spans="1:9">
       <c r="B22">
         <v>12</v>
       </c>
@@ -1684,6 +1690,32 @@
         <v>0</v>
       </c>
       <c r="I22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="B23">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1698,7 +1730,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1709,7 +1741,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -134,10 +134,10 @@
     <t>Topbar</t>
   </si>
   <si>
-    <t>材料编辑栏</t>
-  </si>
-  <si>
-    <t>MaterialModifyBar</t>
+    <t>资源编辑栏</t>
+  </si>
+  <si>
+    <t>ResourceModifyBar</t>
   </si>
   <si>
     <t>对话框(中层)</t>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11610"/>
+    <workbookView windowWidth="29100" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="宋体"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -81,7 +81,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="宋体"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -137,7 +137,7 @@
     <t>材料编辑栏</t>
   </si>
   <si>
-    <t>MaterialModifyBar</t>
+    <t>ResourceModifyBar</t>
   </si>
   <si>
     <t>对话框(中层)</t>
@@ -217,16 +217,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -234,7 +234,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -242,14 +242,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -257,7 +257,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -265,7 +265,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +273,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -281,7 +281,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -289,14 +289,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -304,7 +304,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -312,7 +312,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -320,14 +320,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -335,42 +335,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -678,19 +678,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -828,55 +828,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1175,7 +1175,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
     <col min="3" max="3" width="15.125" customWidth="1"/>
@@ -1183,11 +1183,11 @@
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="25.5" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="19.2583333333333" customWidth="1"/>
-    <col min="9" max="9" width="16.6333333333333" customWidth="1"/>
+    <col min="8" max="8" width="19.2578125" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" ht="17" spans="1:9">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -1281,7 +1281,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="2:9">
       <c r="B6">
         <v>1</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="2:9">
       <c r="B7">
         <v>2</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="2:9">
       <c r="B8">
         <v>3</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="2:9">
       <c r="B9">
         <v>4</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:9">
+    <row r="10" customFormat="1" spans="2:9">
       <c r="B10">
         <v>13</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1421,7 +1421,7 @@
       <c r="C11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="2:9">
       <c r="B12">
         <v>5</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="2:9">
       <c r="B13">
         <v>6</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="2:9">
       <c r="B14">
         <v>7</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="2:9">
       <c r="B15">
         <v>8</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="2:9">
       <c r="B16">
         <v>9</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="2:9">
       <c r="B21">
         <v>10</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="2:9">
       <c r="B22">
         <v>12</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="2:9">
       <c r="B23">
         <v>16</v>
       </c>
@@ -1730,7 +1730,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1741,7 +1741,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
   <si>
     <t>#</t>
   </si>
@@ -210,6 +210,12 @@
   </si>
   <si>
     <t>CardUIForm</t>
+  </si>
+  <si>
+    <t>小地图</t>
+  </si>
+  <si>
+    <t>MinimapUI</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1716,6 +1722,32 @@
         <v>0</v>
       </c>
       <c r="I23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="B24">
+        <v>17</v>
+      </c>
+      <c r="C24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13380"/>
+    <workbookView windowWidth="28800" windowHeight="11610"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
   <si>
     <t>#</t>
   </si>
@@ -71,7 +71,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -81,7 +81,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -210,6 +210,12 @@
   </si>
   <si>
     <t>CardUIForm</t>
+  </si>
+  <si>
+    <t>MinMap</t>
+  </si>
+  <si>
+    <t>MinimapUI</t>
   </si>
 </sst>
 </file>
@@ -217,16 +223,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -234,7 +240,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -242,14 +248,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -257,7 +263,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -265,7 +271,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +279,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -281,7 +287,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -289,14 +295,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -304,7 +310,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -312,7 +318,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -320,14 +326,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -335,42 +341,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -678,19 +684,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -828,55 +834,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1174,8 +1180,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
     <col min="3" max="3" width="15.125" customWidth="1"/>
@@ -1183,11 +1189,11 @@
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="25.5" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="19.2578125" customWidth="1"/>
-    <col min="9" max="9" width="16.6328125" customWidth="1"/>
+    <col min="8" max="8" width="19.2583333333333" customWidth="1"/>
+    <col min="9" max="9" width="16.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1221,7 +1227,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:9">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1270,7 +1276,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -1281,7 +1287,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="2:9">
+    <row r="6" spans="1:9">
       <c r="B6">
         <v>1</v>
       </c>
@@ -1307,7 +1313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:9">
+    <row r="7" spans="1:9">
       <c r="B7">
         <v>2</v>
       </c>
@@ -1333,7 +1339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="1:9">
       <c r="B8">
         <v>3</v>
       </c>
@@ -1359,7 +1365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="1:9">
       <c r="B9">
         <v>4</v>
       </c>
@@ -1385,7 +1391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="2:9">
+    <row r="10" customFormat="1" spans="1:9">
       <c r="B10">
         <v>13</v>
       </c>
@@ -1411,7 +1417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1421,7 +1427,7 @@
       <c r="C11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="1:9">
       <c r="B12">
         <v>5</v>
       </c>
@@ -1447,7 +1453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="1:9">
       <c r="B13">
         <v>6</v>
       </c>
@@ -1473,7 +1479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="1:9">
       <c r="B14">
         <v>7</v>
       </c>
@@ -1499,7 +1505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:9">
+    <row r="15" spans="1:9">
       <c r="B15">
         <v>8</v>
       </c>
@@ -1525,7 +1531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:9">
+    <row r="16" spans="1:9">
       <c r="B16">
         <v>9</v>
       </c>
@@ -1632,7 +1638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -1641,7 +1647,7 @@
       </c>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="2:9">
+    <row r="21" spans="1:9">
       <c r="B21">
         <v>10</v>
       </c>
@@ -1667,7 +1673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:9">
+    <row r="22" spans="1:9">
       <c r="B22">
         <v>12</v>
       </c>
@@ -1693,7 +1699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:9">
+    <row r="23" spans="1:9">
       <c r="B23">
         <v>16</v>
       </c>
@@ -1716,6 +1722,32 @@
         <v>0</v>
       </c>
       <c r="I23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="B24">
+        <v>17</v>
+      </c>
+      <c r="C24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1730,7 +1762,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1741,7 +1773,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11610"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
   <si>
     <t>#</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>MinimapUI</t>
+  </si>
+  <si>
+    <t>FogOfWarUIForm</t>
   </si>
 </sst>
 </file>
@@ -1180,7 +1183,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1748,6 +1751,32 @@
         <v>0</v>
       </c>
       <c r="I24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="B25">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -218,7 +218,7 @@
     <t>MinimapUI</t>
   </si>
   <si>
-    <t>FogOfWarUIForm</t>
+    <t>FogUI</t>
   </si>
 </sst>
 </file>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
   <si>
     <t>#</t>
   </si>
@@ -138,6 +138,12 @@
   </si>
   <si>
     <t>ResourceModifyBar</t>
+  </si>
+  <si>
+    <t>人口栏</t>
+  </si>
+  <si>
+    <t>SupplyUIForm</t>
   </si>
   <si>
     <t>对话框(中层)</t>
@@ -1186,7 +1192,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="13.1272727272727" customWidth="1"/>
@@ -1423,53 +1429,53 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="1" t="s">
+    <row r="11" customFormat="1" spans="1:9">
+      <c r="B11">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
+      <c r="C12" s="1"/>
+      <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:9">
       <c r="B13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
         <v>34</v>
       </c>
       <c r="F13" t="b">
@@ -1487,7 +1493,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="B14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>35</v>
@@ -1495,7 +1501,7 @@
       <c r="D14">
         <v>2</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F14" t="b">
@@ -1513,13 +1519,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="B15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="s">
         <v>38</v>
@@ -1531,7 +1537,7 @@
         <v>2</v>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -1539,40 +1545,39 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
         <v>40</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>2</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1">
-        <v>11</v>
+      <c r="B17">
+        <v>9</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="s">
         <v>42</v>
@@ -1593,7 +1598,7 @@
     <row r="18" spans="1:9">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>43</v>
@@ -1620,13 +1625,13 @@
     <row r="19" spans="1:9">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="s">
         <v>46</v>
@@ -1638,56 +1643,57 @@
         <v>2</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1">
+        <v>15</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="1"/>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="B21">
-        <v>10</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>3</v>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
+      <c r="C21" s="1"/>
     </row>
     <row r="22" spans="1:9">
       <c r="B22">
-        <v>12</v>
-      </c>
-      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
         <v>51</v>
@@ -1707,13 +1713,13 @@
     </row>
     <row r="23" spans="1:9">
       <c r="B23">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
         <v>52</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="s">
         <v>53</v>
@@ -1722,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -1733,7 +1739,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="B24">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" t="s">
         <v>54</v>
@@ -1759,13 +1765,13 @@
     </row>
     <row r="25" spans="1:9">
       <c r="B25">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
         <v>56</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" t="s">
         <v>57</v>
@@ -1780,6 +1786,32 @@
         <v>0</v>
       </c>
       <c r="I25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="B26">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
   <si>
     <t>#</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>SupplyUIForm</t>
+  </si>
+  <si>
+    <t>侧边提示</t>
+  </si>
+  <si>
+    <t>SideTipsUIForm</t>
   </si>
   <si>
     <t>对话框(中层)</t>
@@ -1198,7 +1204,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="13.1272727272727" customWidth="1"/>
@@ -1461,53 +1467,53 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
+    <row r="12" customFormat="1" spans="1:9">
+      <c r="B12">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-      <c r="H13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
+      <c r="C13" s="1"/>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
         <v>36</v>
       </c>
       <c r="F14" t="b">
@@ -1525,7 +1531,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="B15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>37</v>
@@ -1533,7 +1539,7 @@
       <c r="D15">
         <v>2</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F15" t="b">
@@ -1551,13 +1557,13 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="s">
         <v>40</v>
@@ -1569,7 +1575,7 @@
         <v>2</v>
       </c>
       <c r="H16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -1577,40 +1583,39 @@
     </row>
     <row r="17" spans="1:9">
       <c r="B17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="s">
         <v>42</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17">
         <v>2</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1">
-        <v>11</v>
+      <c r="B18">
+        <v>9</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="s">
         <v>44</v>
@@ -1631,7 +1636,7 @@
     <row r="19" spans="1:9">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>45</v>
@@ -1658,13 +1663,13 @@
     <row r="20" spans="1:9">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="s">
         <v>48</v>
@@ -1676,56 +1681,57 @@
         <v>2</v>
       </c>
       <c r="H20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1">
+        <v>15</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="1"/>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="B22">
-        <v>10</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>3</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
+      <c r="C22" s="1"/>
     </row>
     <row r="23" spans="1:9">
       <c r="B23">
-        <v>12</v>
-      </c>
-      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="s">
         <v>53</v>
@@ -1745,13 +1751,13 @@
     </row>
     <row r="24" spans="1:9">
       <c r="B24">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
         <v>54</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="s">
         <v>55</v>
@@ -1760,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -1771,7 +1777,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="B25">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
         <v>56</v>
@@ -1797,13 +1803,13 @@
     </row>
     <row r="26" spans="1:9">
       <c r="B26">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
         <v>58</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" t="s">
         <v>59</v>
@@ -1823,13 +1829,13 @@
     </row>
     <row r="27" spans="1:9">
       <c r="B27">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
         <v>60</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" t="s">
         <v>61</v>
@@ -1844,6 +1850,32 @@
         <v>0</v>
       </c>
       <c r="I27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="B28">
+        <v>20</v>
+      </c>
+      <c r="C28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="66">
   <si>
     <t>#</t>
   </si>
@@ -150,6 +150,12 @@
   </si>
   <si>
     <t>SideTipsUIForm</t>
+  </si>
+  <si>
+    <t>局内顶部界面</t>
+  </si>
+  <si>
+    <t>InGameUIForm</t>
   </si>
   <si>
     <t>对话框(中层)</t>
@@ -1204,7 +1210,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="13.1272727272727" customWidth="1"/>
@@ -1493,53 +1499,53 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="1" t="s">
+    <row r="13" customFormat="1" spans="1:9">
+      <c r="B13">
+        <v>22</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="B14">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
+      <c r="C14" s="1"/>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:9">
       <c r="B15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
         <v>38</v>
       </c>
       <c r="F15" t="b">
@@ -1557,7 +1563,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>39</v>
@@ -1565,7 +1571,7 @@
       <c r="D16">
         <v>2</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>40</v>
       </c>
       <c r="F16" t="b">
@@ -1583,13 +1589,13 @@
     </row>
     <row r="17" spans="1:9">
       <c r="B17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="s">
         <v>42</v>
@@ -1601,7 +1607,7 @@
         <v>2</v>
       </c>
       <c r="H17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -1609,40 +1615,39 @@
     </row>
     <row r="18" spans="1:9">
       <c r="B18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="s">
         <v>44</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="H18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1">
-        <v>11</v>
+      <c r="B19">
+        <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="s">
         <v>46</v>
@@ -1663,7 +1668,7 @@
     <row r="20" spans="1:9">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>47</v>
@@ -1690,13 +1695,13 @@
     <row r="21" spans="1:9">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="s">
         <v>50</v>
@@ -1708,56 +1713,57 @@
         <v>2</v>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1">
+        <v>15</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="1"/>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="B23">
-        <v>10</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>3</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23" t="b">
-        <v>0</v>
-      </c>
+      <c r="C23" s="1"/>
     </row>
     <row r="24" spans="1:9">
       <c r="B24">
-        <v>12</v>
-      </c>
-      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" t="s">
         <v>55</v>
@@ -1777,13 +1783,13 @@
     </row>
     <row r="25" spans="1:9">
       <c r="B25">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
         <v>56</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="s">
         <v>57</v>
@@ -1792,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -1803,7 +1809,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="B26">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26" t="s">
         <v>58</v>
@@ -1829,13 +1835,13 @@
     </row>
     <row r="27" spans="1:9">
       <c r="B27">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
         <v>60</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="s">
         <v>61</v>
@@ -1855,13 +1861,13 @@
     </row>
     <row r="28" spans="1:9">
       <c r="B28">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
         <v>62</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" t="s">
         <v>63</v>
@@ -1876,6 +1882,32 @@
         <v>0</v>
       </c>
       <c r="I28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="B29">
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="72">
   <si>
     <t>#</t>
   </si>
@@ -158,6 +158,12 @@
     <t>InGameUIForm</t>
   </si>
   <si>
+    <t>行动目标</t>
+  </si>
+  <si>
+    <t>GoalUIForm</t>
+  </si>
+  <si>
     <t>对话框(中层)</t>
   </si>
   <si>
@@ -246,6 +252,18 @@
   </si>
   <si>
     <t>FogUI</t>
+  </si>
+  <si>
+    <t>建筑建造面板</t>
+  </si>
+  <si>
+    <t>BuildingBuildTips</t>
+  </si>
+  <si>
+    <t>建筑信息/升级面板</t>
+  </si>
+  <si>
+    <t>BuildingInfoAndUpgradeTips</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1228,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="13.1272727272727" customWidth="1"/>
@@ -1525,53 +1543,53 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
+    <row r="14" customFormat="1" spans="1:9">
+      <c r="B14">
+        <v>23</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="B15">
-        <v>5</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
+      <c r="C15" s="1"/>
+      <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:9">
       <c r="B16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
         <v>40</v>
       </c>
       <c r="F16" t="b">
@@ -1589,7 +1607,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="B17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>41</v>
@@ -1597,7 +1615,7 @@
       <c r="D17">
         <v>2</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F17" t="b">
@@ -1615,13 +1633,13 @@
     </row>
     <row r="18" spans="1:9">
       <c r="B18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="s">
         <v>44</v>
@@ -1633,7 +1651,7 @@
         <v>2</v>
       </c>
       <c r="H18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -1641,40 +1659,39 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="s">
         <v>46</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
         <v>2</v>
       </c>
       <c r="H19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1">
-        <v>11</v>
+      <c r="B20">
+        <v>9</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="s">
         <v>48</v>
@@ -1695,7 +1712,7 @@
     <row r="21" spans="1:9">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>49</v>
@@ -1722,13 +1739,13 @@
     <row r="22" spans="1:9">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
         <v>52</v>
@@ -1740,56 +1757,57 @@
         <v>2</v>
       </c>
       <c r="H22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1">
+        <v>15</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="1"/>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="B24">
-        <v>10</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>3</v>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24" t="b">
-        <v>0</v>
-      </c>
+      <c r="C24" s="1"/>
     </row>
     <row r="25" spans="1:9">
       <c r="B25">
-        <v>12</v>
-      </c>
-      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="s">
         <v>57</v>
@@ -1809,13 +1827,13 @@
     </row>
     <row r="26" spans="1:9">
       <c r="B26">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
         <v>58</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="s">
         <v>59</v>
@@ -1824,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -1835,7 +1853,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="B27">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" t="s">
         <v>60</v>
@@ -1861,13 +1879,13 @@
     </row>
     <row r="28" spans="1:9">
       <c r="B28">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" t="s">
         <v>62</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" t="s">
         <v>63</v>
@@ -1887,13 +1905,13 @@
     </row>
     <row r="29" spans="1:9">
       <c r="B29">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
         <v>64</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="s">
         <v>65</v>
@@ -1908,6 +1926,84 @@
         <v>0</v>
       </c>
       <c r="I29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="B30">
+        <v>20</v>
+      </c>
+      <c r="C30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:9">
+      <c r="B31">
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>69</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>3</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:9">
+      <c r="B32">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>3</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="74">
   <si>
     <t>#</t>
   </si>
@@ -260,10 +260,16 @@
     <t>BuildingBuildTips</t>
   </si>
   <si>
-    <t>建筑信息/升级面板</t>
-  </si>
-  <si>
-    <t>BuildingInfoAndUpgradeTips</t>
+    <t>建筑升级面板</t>
+  </si>
+  <si>
+    <t>BuildingUpgradeTips</t>
+  </si>
+  <si>
+    <t>建筑信息面板</t>
+  </si>
+  <si>
+    <t>BuildingInfoTips</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1234,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="13.1272727272727" customWidth="1"/>
@@ -2004,6 +2010,32 @@
         <v>0</v>
       </c>
       <c r="I32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="2:9">
+      <c r="B33">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>3</v>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="76">
   <si>
     <t>#</t>
   </si>
@@ -270,6 +270,12 @@
   </si>
   <si>
     <t>BuildingInfoTips</t>
+  </si>
+  <si>
+    <t>选关面板</t>
+  </si>
+  <si>
+    <t>LevelSwitchUIForm</t>
   </si>
 </sst>
 </file>
@@ -1234,7 +1240,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="13.1272727272727" customWidth="1"/>
@@ -1401,7 +1407,7 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E8" t="s">
         <v>25</v>
@@ -2037,6 +2043,32 @@
       </c>
       <c r="I33" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="2:9">
+      <c r="B34">
+        <v>27</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34">
+        <v>6</v>
+      </c>
+      <c r="E34" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -95,7 +95,7 @@
     <t>显示顺序,相对于Group,每个Group间隔100</t>
   </si>
   <si>
-    <t>同组界面被覆盖时是否隐藏</t>
+    <t>覆盖同组界面时是否隐藏对方</t>
   </si>
   <si>
     <t>UI组Id</t>
@@ -122,97 +122,127 @@
     <t>GameUIForm</t>
   </si>
   <si>
+    <t>顶部资源栏</t>
+  </si>
+  <si>
+    <t>Topbar</t>
+  </si>
+  <si>
+    <t>材料编辑栏</t>
+  </si>
+  <si>
+    <t>ResourceModifyBar</t>
+  </si>
+  <si>
+    <t>人口栏</t>
+  </si>
+  <si>
+    <t>SupplyUIForm</t>
+  </si>
+  <si>
+    <t>侧边提示</t>
+  </si>
+  <si>
+    <t>SideTipsUIForm</t>
+  </si>
+  <si>
+    <t>局内顶部界面</t>
+  </si>
+  <si>
+    <t>InGameUIForm</t>
+  </si>
+  <si>
+    <t>行动目标</t>
+  </si>
+  <si>
+    <t>GoalUIForm</t>
+  </si>
+  <si>
+    <t>卡牌面板</t>
+  </si>
+  <si>
+    <t>CardUIForm</t>
+  </si>
+  <si>
+    <t>小地图</t>
+  </si>
+  <si>
+    <t>MinimapUI</t>
+  </si>
+  <si>
+    <t>阶段切换按钮</t>
+  </si>
+  <si>
+    <t>PhaseSwitchUIForm</t>
+  </si>
+  <si>
+    <t>迷雾UI</t>
+  </si>
+  <si>
+    <t>FogUI</t>
+  </si>
+  <si>
+    <t>对话框(中层)</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>SettingDialog</t>
+  </si>
+  <si>
+    <t>评分</t>
+  </si>
+  <si>
+    <t>RatingDialog</t>
+  </si>
+  <si>
+    <t>服务条款</t>
+  </si>
+  <si>
+    <t>TermsOfServiceDialog</t>
+  </si>
+  <si>
+    <t>通用提示对话框</t>
+  </si>
+  <si>
+    <t>CommonDialog</t>
+  </si>
+  <si>
+    <t>语言设置</t>
+  </si>
+  <si>
+    <t>LanguagesDialog</t>
+  </si>
+  <si>
+    <t>合成面板</t>
+  </si>
+  <si>
+    <t>CraftingDialog</t>
+  </si>
+  <si>
+    <t>科技树</t>
+  </si>
+  <si>
+    <t>TechTreeDialog</t>
+  </si>
+  <si>
+    <t>科技节点详情</t>
+  </si>
+  <si>
+    <t>TechNodeDetailTips</t>
+  </si>
+  <si>
     <t>游戏结算</t>
   </si>
   <si>
     <t>GameOverUIForm</t>
   </si>
   <si>
-    <t>顶部资源栏</t>
-  </si>
-  <si>
-    <t>Topbar</t>
-  </si>
-  <si>
-    <t>材料编辑栏</t>
-  </si>
-  <si>
-    <t>ResourceModifyBar</t>
-  </si>
-  <si>
-    <t>人口栏</t>
-  </si>
-  <si>
-    <t>SupplyUIForm</t>
-  </si>
-  <si>
-    <t>侧边提示</t>
-  </si>
-  <si>
-    <t>SideTipsUIForm</t>
-  </si>
-  <si>
-    <t>局内顶部界面</t>
-  </si>
-  <si>
-    <t>InGameUIForm</t>
-  </si>
-  <si>
-    <t>行动目标</t>
-  </si>
-  <si>
-    <t>GoalUIForm</t>
-  </si>
-  <si>
-    <t>对话框(中层)</t>
-  </si>
-  <si>
-    <t>设置</t>
-  </si>
-  <si>
-    <t>SettingDialog</t>
-  </si>
-  <si>
-    <t>评分</t>
-  </si>
-  <si>
-    <t>RatingDialog</t>
-  </si>
-  <si>
-    <t>服务条款</t>
-  </si>
-  <si>
-    <t>TermsOfServiceDialog</t>
-  </si>
-  <si>
-    <t>通用提示对话框</t>
-  </si>
-  <si>
-    <t>CommonDialog</t>
-  </si>
-  <si>
-    <t>语言设置</t>
-  </si>
-  <si>
-    <t>LanguagesDialog</t>
-  </si>
-  <si>
-    <t>合成面板</t>
-  </si>
-  <si>
-    <t>CraftingDialog</t>
-  </si>
-  <si>
-    <t>科技树</t>
-  </si>
-  <si>
-    <t>TechTreeDialog</t>
-  </si>
-  <si>
-    <t>科技节点详情</t>
-  </si>
-  <si>
-    <t>TechNodeDetailTips</t>
+    <t>选关面板</t>
+  </si>
+  <si>
+    <t>LevelSwitchUIForm</t>
   </si>
   <si>
     <t>提示(顶层)</t>
@@ -230,30 +260,6 @@
     <t>InteractOptionTips</t>
   </si>
   <si>
-    <t>卡牌面板</t>
-  </si>
-  <si>
-    <t>CardUIForm</t>
-  </si>
-  <si>
-    <t>小地图</t>
-  </si>
-  <si>
-    <t>MinimapUI</t>
-  </si>
-  <si>
-    <t>阶段切换按钮</t>
-  </si>
-  <si>
-    <t>PhaseSwitchUIForm</t>
-  </si>
-  <si>
-    <t>迷雾UI</t>
-  </si>
-  <si>
-    <t>FogUI</t>
-  </si>
-  <si>
     <t>建筑建造面板</t>
   </si>
   <si>
@@ -270,12 +276,6 @@
   </si>
   <si>
     <t>BuildingInfoTips</t>
-  </si>
-  <si>
-    <t>选关面板</t>
-  </si>
-  <si>
-    <t>LevelSwitchUIForm</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1247,7 @@
     <col min="3" max="3" width="15.1272727272727" customWidth="1"/>
     <col min="4" max="4" width="40.1272727272727" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="25.5" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
     <col min="8" max="8" width="19.2545454545455" customWidth="1"/>
     <col min="9" max="9" width="16.6363636363636" customWidth="1"/>
@@ -1401,19 +1401,19 @@
     </row>
     <row r="8" spans="1:9">
       <c r="B8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D8">
-        <v>5</v>
-      </c>
-      <c r="E8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1422,12 +1422,12 @@
         <v>0</v>
       </c>
       <c r="I8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:9">
       <c r="B9">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>26</v>
@@ -1453,13 +1453,13 @@
     </row>
     <row r="10" customFormat="1" spans="1:9">
       <c r="B10">
-        <v>13</v>
-      </c>
-      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
         <v>28</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>29</v>
@@ -1479,13 +1479,13 @@
     </row>
     <row r="11" customFormat="1" spans="1:9">
       <c r="B11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>31</v>
@@ -1505,15 +1505,15 @@
     </row>
     <row r="12" customFormat="1" spans="1:9">
       <c r="B12">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D12">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
         <v>33</v>
       </c>
       <c r="F12" t="b">
@@ -1531,13 +1531,13 @@
     </row>
     <row r="13" customFormat="1" spans="1:9">
       <c r="B13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="s">
         <v>35</v>
@@ -1555,11 +1555,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="1:9">
+    <row r="14" spans="1:9">
       <c r="B14">
-        <v>23</v>
-      </c>
-      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
         <v>36</v>
       </c>
       <c r="D14">
@@ -1582,102 +1582,102 @@
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="B16">
-        <v>5</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="B17">
-        <v>6</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
       </c>
       <c r="D17">
         <v>2</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>42</v>
+      <c r="E17" t="s">
+        <v>43</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="B18">
-        <v>7</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
+      <c r="C18" s="1"/>
+      <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:9">
       <c r="B19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="s">
         <v>46</v>
@@ -1689,7 +1689,7 @@
         <v>2</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
@@ -1697,7 +1697,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="B20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>47</v>
@@ -1705,11 +1705,11 @@
       <c r="D20">
         <v>2</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1722,21 +1722,20 @@
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1">
-        <v>11</v>
+      <c r="B21">
+        <v>7</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
         <v>50</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1749,36 +1748,34 @@
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1">
-        <v>14</v>
+      <c r="B22">
+        <v>8</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" t="s">
         <v>52</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>2</v>
       </c>
       <c r="H22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1">
-        <v>15</v>
+      <c r="B23">
+        <v>9</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>53</v>
@@ -1796,156 +1793,159 @@
         <v>2</v>
       </c>
       <c r="H23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1">
+        <v>11</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="1"/>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>56</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="B25">
-        <v>10</v>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1">
+        <v>14</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="B26">
-        <v>12</v>
-      </c>
-      <c r="C26" t="s">
-        <v>58</v>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1">
+        <v>15</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D26">
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
       </c>
       <c r="I26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="B27">
-        <v>16</v>
-      </c>
-      <c r="C27" t="s">
-        <v>60</v>
+        <v>3</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
       </c>
       <c r="I27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:9">
       <c r="B28">
-        <v>17</v>
-      </c>
-      <c r="C28" t="s">
-        <v>62</v>
+        <v>27</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="B29">
-        <v>18</v>
-      </c>
-      <c r="C29" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
+      <c r="C29" s="1"/>
     </row>
     <row r="30" spans="1:9">
       <c r="B30">
-        <v>20</v>
-      </c>
-      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>66</v>
       </c>
       <c r="D30">
@@ -1958,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -1967,9 +1967,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" customFormat="1" spans="1:9">
+    <row r="31" spans="1:9">
       <c r="B31">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
         <v>68</v>
@@ -1995,7 +1995,7 @@
     </row>
     <row r="32" customFormat="1" spans="1:9">
       <c r="B32">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
         <v>70</v>
@@ -2007,7 +2007,7 @@
         <v>71</v>
       </c>
       <c r="F32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="33" customFormat="1" spans="2:9">
       <c r="B33">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
         <v>72</v>
@@ -2033,7 +2033,7 @@
         <v>73</v>
       </c>
       <c r="F33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -2047,28 +2047,28 @@
     </row>
     <row r="34" customFormat="1" spans="2:9">
       <c r="B34">
-        <v>27</v>
-      </c>
-      <c r="C34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
         <v>74</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E34" t="s">
         <v>75</v>
       </c>
       <c r="F34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -1897,7 +1897,7 @@
         <v>1</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="78">
   <si>
     <t>#</t>
   </si>
@@ -243,6 +243,12 @@
   </si>
   <si>
     <t>LevelSwitchUIForm</t>
+  </si>
+  <si>
+    <t>关卡tag面板</t>
+  </si>
+  <si>
+    <t>LvEnterDialog</t>
   </si>
   <si>
     <t>提示(顶层)</t>
@@ -1240,7 +1246,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="13.1272727272727" customWidth="1"/>
@@ -1932,50 +1938,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="1" t="s">
+    <row r="29" customFormat="1" spans="1:9">
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="1"/>
+      <c r="D29">
+        <v>5</v>
+      </c>
+      <c r="E29" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>2</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="B30">
-        <v>10</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>3</v>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" t="b">
-        <v>0</v>
-      </c>
+      <c r="C30" s="1"/>
     </row>
     <row r="31" spans="1:9">
       <c r="B31">
-        <v>12</v>
-      </c>
-      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="s">
         <v>69</v>
@@ -1993,9 +1999,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" customFormat="1" spans="1:9">
+    <row r="32" spans="1:9">
       <c r="B32">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
         <v>70</v>
@@ -2007,7 +2013,7 @@
         <v>71</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -2021,7 +2027,7 @@
     </row>
     <row r="33" customFormat="1" spans="2:9">
       <c r="B33">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
         <v>72</v>
@@ -2047,7 +2053,7 @@
     </row>
     <row r="34" customFormat="1" spans="2:9">
       <c r="B34">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
         <v>74</v>
@@ -2068,6 +2074,32 @@
         <v>0</v>
       </c>
       <c r="I34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="2:9">
+      <c r="B35">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>77</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>#</t>
   </si>
@@ -76,7 +76,7 @@
     <t>bool</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -86,7 +86,7 @@
       </rPr>
       <t>i</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -262,21 +262,22 @@
   <si>
     <t>BuildingInfoTips</t>
   </si>
+  <si>
+    <t>Story AVG</t>
+  </si>
+  <si>
+    <t>StoryUIForm</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -304,7 +305,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" applyFont="1" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -609,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.08984375" customWidth="1"/>
@@ -622,71 +623,71 @@
     <col min="9" max="9" width="16.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="0" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="0" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="0" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -701,11 +702,11 @@
       <c r="H4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="0" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -716,267 +717,267 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B6">
+    <row r="6">
+      <c r="B6" s="0">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" s="0">
+        <v>1</v>
+      </c>
+      <c r="E6" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="F6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1</v>
+      </c>
+      <c r="H6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="0">
+        <v>2</v>
+      </c>
+      <c r="C7" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="0">
+        <v>1</v>
+      </c>
+      <c r="E7" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8">
+      <c r="F7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0">
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="0">
         <v>2</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B9">
+      <c r="F8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0">
+        <v>1</v>
+      </c>
+      <c r="H8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0">
         <v>19</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="0">
         <v>3</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B10">
+      <c r="F9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0">
+        <v>1</v>
+      </c>
+      <c r="H9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="0">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="0">
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11">
+      <c r="F10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0">
+        <v>1</v>
+      </c>
+      <c r="H10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="0">
         <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D11" s="0">
+        <v>1</v>
+      </c>
+      <c r="E11" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B12">
+      <c r="F11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0">
+        <v>1</v>
+      </c>
+      <c r="H11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="0">
         <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="0">
         <v>3</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B13">
+      <c r="F12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="0">
+        <v>1</v>
+      </c>
+      <c r="H12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0">
         <v>16</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="0">
         <v>3</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B14">
+      <c r="F13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="0">
+        <v>1</v>
+      </c>
+      <c r="H13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="0">
         <v>17</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D14" s="0">
+        <v>2</v>
+      </c>
+      <c r="E14" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15">
+      <c r="F14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="0">
+        <v>1</v>
+      </c>
+      <c r="H14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="0">
         <v>20</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D15" s="0">
+        <v>2</v>
+      </c>
+      <c r="E15" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="0">
+        <v>1</v>
+      </c>
+      <c r="H15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -986,215 +987,215 @@
       <c r="C16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B17">
+    <row r="17">
+      <c r="B17" s="0">
         <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D17" s="0">
+        <v>1</v>
+      </c>
+      <c r="E17" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="F17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-      <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B18">
+      <c r="F17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0">
+        <v>2</v>
+      </c>
+      <c r="H17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="0">
         <v>6</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="0">
         <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B19">
+      <c r="F18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0">
+        <v>2</v>
+      </c>
+      <c r="H18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0">
         <v>7</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="D19" s="0">
+        <v>2</v>
+      </c>
+      <c r="E19" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="F19" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B20">
+      <c r="F19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="0">
+        <v>2</v>
+      </c>
+      <c r="H19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="0">
         <v>8</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="0">
         <v>3</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B21">
+      <c r="F20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" s="0">
+        <v>2</v>
+      </c>
+      <c r="H20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="0">
         <v>9</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="D21" s="0">
+        <v>2</v>
+      </c>
+      <c r="E21" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B22">
+      <c r="F21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="0">
+        <v>2</v>
+      </c>
+      <c r="H21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="0">
         <v>3</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="0">
         <v>3</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="F22" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B23">
+      <c r="F22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" s="0">
+        <v>2</v>
+      </c>
+      <c r="H22" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="0">
         <v>27</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="0">
         <v>4</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="F23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-      <c r="H23" t="b">
-        <v>1</v>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B24">
+      <c r="F23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0">
+        <v>2</v>
+      </c>
+      <c r="H23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="0">
         <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="0">
         <v>5</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="F24" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>2</v>
-      </c>
-      <c r="H24" t="b">
-        <v>1</v>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0">
+        <v>2</v>
+      </c>
+      <c r="H24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -1203,159 +1204,186 @@
       </c>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B26">
+    <row r="26">
+      <c r="B26" s="0">
         <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="D26" s="0">
+        <v>1</v>
+      </c>
+      <c r="E26" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26">
+      <c r="F26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="0">
         <v>3</v>
       </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B27">
+      <c r="H26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="0">
         <v>12</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="D27">
-        <v>2</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="D27" s="0">
+        <v>2</v>
+      </c>
+      <c r="E27" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27">
+      <c r="F27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="0">
         <v>3</v>
       </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B28">
+      <c r="H27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="0">
         <v>24</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="D28">
-        <v>2</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="D28" s="0">
+        <v>2</v>
+      </c>
+      <c r="E28" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="F28" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28">
+      <c r="F28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="0">
         <v>3</v>
       </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B29">
+      <c r="H28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="0">
         <v>25</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D29">
-        <v>2</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="D29" s="0">
+        <v>2</v>
+      </c>
+      <c r="E29" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29">
+      <c r="F29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="0">
         <v>3</v>
       </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B30">
+      <c r="H29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="0">
         <v>26</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="D30" s="0">
+        <v>2</v>
+      </c>
+      <c r="E30" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="F30" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30">
+      <c r="F30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="0">
         <v>3</v>
       </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" t="b">
-        <v>0</v>
+      <c r="H30" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="0">
+        <v>29</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="0">
+        <v>6</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="F31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="0">
+        <v>2</v>
+      </c>
+      <c r="H31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>